--- a/2026-2027 Attending Call - Vacay_Away Dates.xlsx
+++ b/2026-2027 Attending Call - Vacay_Away Dates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\parav\Documents\Coding Projects\attending_call_schedule\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B38C59-E256-4E4B-B40A-3F06DC2AB01A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA8EEA2-BA41-45D3-90F2-1852F0036CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="101">
   <si>
     <t>Timestamp</t>
   </si>
@@ -365,6 +365,9 @@
   </si>
   <si>
     <t>4/12/27-4/18/27</t>
+  </si>
+  <si>
+    <t>Michelle Abou-Jaoude</t>
   </si>
 </sst>
 </file>
@@ -461,7 +464,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -497,6 +500,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -588,7 +594,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:F19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:F20">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Timestamp"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Please enter your first and last name"/>
@@ -1246,11 +1252,15 @@
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
+      <c r="A20" s="16">
+        <v>46159</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
+      <c r="E20" s="4"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
